--- a/data/trans_dic/P3A$pareja-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P3A$pareja-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que la pareja de la persona entrevistada se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente la pareja de la persona entrevistada se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>42,34; 50,29</t>
+          <t>42,13; 50,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,53; 11,94</t>
+          <t>8,43; 11,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22,64; 26,73</t>
+          <t>22,55; 26,43</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>29,55; 48,12</t>
+          <t>28,4; 48,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,12; 24,5</t>
+          <t>15,76; 24,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25,31; 35,67</t>
+          <t>25,41; 35,61</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>48,99; 57,59</t>
+          <t>49,52; 57,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29,55; 36,17</t>
+          <t>29,21; 35,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>40,28; 45,52</t>
+          <t>40,38; 45,48</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>35,23; 49,17</t>
+          <t>34,02; 49,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,91; 22,87</t>
+          <t>16,84; 22,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28,57; 34,8</t>
+          <t>28,63; 34,78</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que la pareja de la persona entrevistada se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente la pareja de la persona entrevistada se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>218024; 258967</t>
+          <t>216944; 257615</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>64450; 90242</t>
+          <t>63656; 89704</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>287633; 339603</t>
+          <t>286533; 335837</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>676480; 1101577</t>
+          <t>650080; 1102830</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>338098; 548000</t>
+          <t>352565; 547866</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1145531; 1614566</t>
+          <t>1150022; 1611417</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>316753; 372419</t>
+          <t>320237; 374625</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>195177; 238884</t>
+          <t>192914; 234769</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>526529; 595028</t>
+          <t>527803; 594436</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1215714; 1696844</t>
+          <t>1174071; 1690838</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>617497; 835390</t>
+          <t>615246; 832941</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2029413; 2472143</t>
+          <t>2033941; 2470658</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P3A$pareja-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P3A$pareja-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,99%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>42,13; 50,03</t>
+          <t>42,69; 50,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,43; 11,87</t>
+          <t>8,45; 11,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22,55; 26,43</t>
+          <t>22,95; 26,92</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>36,29%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>28,4; 48,17</t>
+          <t>45,99; 50,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,76; 24,5</t>
+          <t>22,19; 25,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25,41; 35,61</t>
+          <t>34,73; 37,68</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>42,66%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>49,52; 57,94</t>
+          <t>50,0; 58,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29,21; 35,55</t>
+          <t>28,57; 34,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>40,38; 45,48</t>
+          <t>40,22; 45,54</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>35,37%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>34,02; 49,0</t>
+          <t>47,35; 51,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,84; 22,8</t>
+          <t>21,23; 23,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28,63; 34,78</t>
+          <t>34,31; 36,52</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>238085</t>
+          <t>269375</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>74934</t>
+          <t>80640</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>313019</t>
+          <t>350015</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>216944; 257615</t>
+          <t>246980; 291648</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>63656; 89704</t>
+          <t>69430; 96124</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>286533; 335837</t>
+          <t>321368; 377075</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>968519</t>
+          <t>1078680</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>475220</t>
+          <t>517731</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1443739</t>
+          <t>1596411</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>650080; 1102830</t>
+          <t>1025435; 1131674</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>352565; 547866</t>
+          <t>481597; 552899</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1150022; 1611417</t>
+          <t>1528205; 1657934</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>345493</t>
+          <t>385234</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>214905</t>
+          <t>231777</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>560398</t>
+          <t>617011</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>320237; 374625</t>
+          <t>355763; 413348</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>192914; 234769</t>
+          <t>209987; 255412</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>527803; 594436</t>
+          <t>581765; 658700</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1552098</t>
+          <t>1733290</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>765059</t>
+          <t>830148</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2317157</t>
+          <t>2563438</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1174071; 1690838</t>
+          <t>1666500; 1799797</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>615246; 832941</t>
+          <t>791284; 872626</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2033941; 2470658</t>
+          <t>2485991; 2646137</t>
         </is>
       </c>
     </row>
